--- a/translate-PL.xlsx
+++ b/translate-PL.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B316"/>
+  <dimension ref="A1:B317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4209,6 +4209,18 @@
       <c r="B316" t="inlineStr">
         <is>
           <t>LPO 25 + SZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Dětská postel DOPLO PINE s přistýlkou, zábranou, rošty  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>LPW 01 + SZ</t>
         </is>
       </c>
     </row>

--- a/translate-PL.xlsx
+++ b/translate-PL.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B317"/>
+  <dimension ref="A1:B318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4221,6 +4221,18 @@
       <c r="B317" t="inlineStr">
         <is>
           <t>LPW 01 + SZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Patrová postel ELEGANT PINE z masivní borovice – včetně roštů  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>LP 02 + SZ</t>
         </is>
       </c>
     </row>

--- a/translate-PL.xlsx
+++ b/translate-PL.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B318"/>
+  <dimension ref="A1:B319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4233,6 +4233,18 @@
       <c r="B318" t="inlineStr">
         <is>
           <t>LP 02 + SZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Dětská postel ROBIN PINE z masivní borovice se zábranou, roštem  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>LPO 05 + SZ</t>
         </is>
       </c>
     </row>

--- a/translate-PL.xlsx
+++ b/translate-PL.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B319"/>
+  <dimension ref="A1:B320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4245,6 +4245,18 @@
       <c r="B319" t="inlineStr">
         <is>
           <t>LPO 05 + SZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Dětská postel ALEXANDER PINE z masivu vč. roštu  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>LPO 10 + SZ</t>
         </is>
       </c>
     </row>

--- a/translate-PL.xlsx
+++ b/translate-PL.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B320"/>
+  <dimension ref="A1:B321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4257,6 +4257,18 @@
       <c r="B320" t="inlineStr">
         <is>
           <t>LPO 10 + SZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Dětská postel s přistýlkou MAREK PINE z masivu borovice 90x200 cm včetně roštů  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>LPW 03 + SZ</t>
         </is>
       </c>
     </row>

--- a/translate-PL.xlsx
+++ b/translate-PL.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B321"/>
+  <dimension ref="A1:B322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4269,6 +4269,18 @@
       <c r="B321" t="inlineStr">
         <is>
           <t>LPW 03 + SZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Dětská postel DP08  + ÚLOŽNÉ PROSTORY ZDARMA!</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>LPO 08 + SZ</t>
         </is>
       </c>
     </row>

--- a/translate-PL.xlsx
+++ b/translate-PL.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B322"/>
+  <dimension ref="A1:B323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4281,6 +4281,18 @@
       <c r="B322" t="inlineStr">
         <is>
           <t>LPO 08 + SZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Dětská postel DP05, se zábranou  + ÚLOŽNÉ PROSTORY ZDARMA!</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>LPO 05 + SZ</t>
         </is>
       </c>
     </row>

--- a/translate-PL.xlsx
+++ b/translate-PL.xlsx
@@ -4307,7 +4307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B510"/>
+  <dimension ref="A1:B511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10427,6 +10427,18 @@
       <c r="B510" t="inlineStr">
         <is>
           <t>kaszmir, 80 x 180 cm</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>Zvolte barvu:: bezbarvý lak, Zvolte rozměr:: 80/120 x 200 cm, Žebřík: vlevo (vyobrazeno)</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>lakier, 80/120 x 200 cm, drabinka wlewo</t>
         </is>
       </c>
     </row>

--- a/translate-PL.xlsx
+++ b/translate-PL.xlsx
@@ -4307,7 +4307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B511"/>
+  <dimension ref="A1:B512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10439,6 +10439,18 @@
       <c r="B511" t="inlineStr">
         <is>
           <t>lakier, 80/120 x 200 cm, drabinka wlewo</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>Zvolte barvu:: barva hnědá, Zvolte rozměr:: 90 x 190 cm</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>braz, 90 x 190 cm</t>
         </is>
       </c>
     </row>

--- a/translate-PL.xlsx
+++ b/translate-PL.xlsx
@@ -4307,7 +4307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B512"/>
+  <dimension ref="A1:B513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10451,6 +10451,18 @@
       <c r="B512" t="inlineStr">
         <is>
           <t>braz, 90 x 190 cm</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>Zvolte barvu:: barva bílá</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>bialy</t>
         </is>
       </c>
     </row>

--- a/translate-PL.xlsx
+++ b/translate-PL.xlsx
@@ -4307,7 +4307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B513"/>
+  <dimension ref="A1:B514"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10463,6 +10463,18 @@
       <c r="B513" t="inlineStr">
         <is>
           <t>bialy</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>Zvolte barvu:: barva kašmír, Zvolte rozměr:: 90 x 200 cm</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>kaszmir, 90 x 200 cm</t>
         </is>
       </c>
     </row>

--- a/translate-PL.xlsx
+++ b/translate-PL.xlsx
@@ -4307,7 +4307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B514"/>
+  <dimension ref="A1:B515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10475,6 +10475,18 @@
       <c r="B514" t="inlineStr">
         <is>
           <t>kaszmir, 90 x 200 cm</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>Zvolte barvu:: barva olivová, Zvolte rozměr:: 140 x 200 cm</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>oliwkowy, 140 x 200 cm</t>
         </is>
       </c>
     </row>

--- a/translate-PL.xlsx
+++ b/translate-PL.xlsx
@@ -4307,7 +4307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B515"/>
+  <dimension ref="A1:B516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10487,6 +10487,18 @@
       <c r="B515" t="inlineStr">
         <is>
           <t>oliwkowy, 140 x 200 cm</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>Zvolte barvu:: barva olivová</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>oliwkowy</t>
         </is>
       </c>
     </row>

--- a/translate-PL.xlsx
+++ b/translate-PL.xlsx
@@ -4307,7 +4307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B516"/>
+  <dimension ref="A1:B517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10499,6 +10499,18 @@
       <c r="B516" t="inlineStr">
         <is>
           <t>oliwkowy</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>Zvolte barvu:: barva grafit, Zvolte rozměr:: 90/140 x 200 cm, Žebřík: vlevo (vyobrazeno)</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>grafit, 90/140 x 200 cm, drabinka wlewo</t>
         </is>
       </c>
     </row>

--- a/translate-PL.xlsx
+++ b/translate-PL.xlsx
@@ -4307,7 +4307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B517"/>
+  <dimension ref="A1:B518"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10511,6 +10511,18 @@
       <c r="B517" t="inlineStr">
         <is>
           <t>grafit, 90/140 x 200 cm, drabinka wlewo</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>Zvolte barvu:: surové dřevo, Zvolte rozměr:: 70 x 140 cm</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>surowa-b, 70 x 140 cm</t>
         </is>
       </c>
     </row>

--- a/translate-PL.xlsx
+++ b/translate-PL.xlsx
@@ -4307,7 +4307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B518"/>
+  <dimension ref="A1:B519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10523,6 +10523,18 @@
       <c r="B518" t="inlineStr">
         <is>
           <t>surowa-b, 70 x 140 cm</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>Zvolte barvu:: barva růžová, Zvolte rozměr:: 80 x 190 cm</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>rozowy, 80 x 190 cm</t>
         </is>
       </c>
     </row>

--- a/translate-PL.xlsx
+++ b/translate-PL.xlsx
@@ -4307,7 +4307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B519"/>
+  <dimension ref="A1:B520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10535,6 +10535,18 @@
       <c r="B519" t="inlineStr">
         <is>
           <t>rozowy, 80 x 190 cm</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>Zvolte barvu:: barva olivová, Zvolte rozměr:: 120 x 200 cm</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>oliwkowy, 120 x 200 cm</t>
         </is>
       </c>
     </row>

--- a/translate-PL.xlsx
+++ b/translate-PL.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B323"/>
+  <dimension ref="A1:B324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4293,6 +4293,18 @@
       <c r="B323" t="inlineStr">
         <is>
           <t>LPO 05 + SZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Dětská postel s přistýlkou, úložným prostorem a zábranou OTAN PINE masiv borovic</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>LPW 01 + SZ</t>
         </is>
       </c>
     </row>

--- a/translate-PL.xlsx
+++ b/translate-PL.xlsx
@@ -4319,7 +4319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B520"/>
+  <dimension ref="A1:B521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10559,6 +10559,18 @@
       <c r="B520" t="inlineStr">
         <is>
           <t>oliwkowy, 120 x 200 cm</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>Barva: Bezbarvý lak, Rozměr: 90 x 200 cm</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>lakier, 90 x 200 cm</t>
         </is>
       </c>
     </row>

--- a/translate-PL.xlsx
+++ b/translate-PL.xlsx
@@ -4319,7 +4319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B521"/>
+  <dimension ref="A1:B522"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10571,6 +10571,18 @@
       <c r="B521" t="inlineStr">
         <is>
           <t>lakier, 90 x 200 cm</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>Barva: Surové dřevo, Rozměr: 90 x 200 cm</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>surowa-b, 90 x 200 cm</t>
         </is>
       </c>
     </row>

--- a/translate-PL.xlsx
+++ b/translate-PL.xlsx
@@ -4319,7 +4319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B522"/>
+  <dimension ref="A1:B523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10583,6 +10583,18 @@
       <c r="B522" t="inlineStr">
         <is>
           <t>surowa-b, 90 x 200 cm</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>Barva: Bezbarvý lak, Rozměr: 80 x 200 cm</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>lakier, 80 x 200 cm</t>
         </is>
       </c>
     </row>

--- a/translate-PL.xlsx
+++ b/translate-PL.xlsx
@@ -4319,7 +4319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B523"/>
+  <dimension ref="A1:B524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10595,6 +10595,18 @@
       <c r="B523" t="inlineStr">
         <is>
           <t>lakier, 80 x 200 cm</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>Barva: Bezbarvý lak, Rozměr: 90 x 180 cm</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>lakier, 90 x 180 cm</t>
         </is>
       </c>
     </row>

--- a/translate-PL.xlsx
+++ b/translate-PL.xlsx
@@ -11249,7 +11249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B104"/>
+  <dimension ref="A1:B105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12500,6 +12500,18 @@
         </is>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>DPT 01 + SZ</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/translate-PL.xlsx
+++ b/translate-PL.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B324"/>
+  <dimension ref="A1:B325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4305,6 +4305,18 @@
       <c r="B324" t="inlineStr">
         <is>
           <t>LPW 01 + SZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Dětská postel MAXIM PINE s přistýlkou z masivu včetně roštů  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>LPW 10 + SZ</t>
         </is>
       </c>
     </row>

--- a/translate-PL.xlsx
+++ b/translate-PL.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B325"/>
+  <dimension ref="A1:B326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4317,6 +4317,18 @@
       <c r="B325" t="inlineStr">
         <is>
           <t>LPW 10 + SZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Dětská postel s přistýlkou OTTO PINE z masivu borovice, se zábranou, rošty  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>LPW 04 + SZ</t>
         </is>
       </c>
     </row>

--- a/translate-PL.xlsx
+++ b/translate-PL.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B326"/>
+  <dimension ref="A1:B327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4329,6 +4329,18 @@
       <c r="B326" t="inlineStr">
         <is>
           <t>LPW 04 + SZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Dětská postel RENE se zábranou proti pádu – 120x200, 140x200, 160x200 cm s roštem</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>LPO 34</t>
         </is>
       </c>
     </row>

--- a/translate-PL.xlsx
+++ b/translate-PL.xlsx
@@ -4355,7 +4355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B524"/>
+  <dimension ref="A1:B525"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10643,6 +10643,18 @@
       <c r="B524" t="inlineStr">
         <is>
           <t>lakier, 90 x 180 cm</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>Zvolte barvu:: barva grafit, Zvolte rozměr:: 80/120 x 200 cm, Žebřík: vlevo (vyobrazeno)</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>grafit, 80/120 x 200 cm, drabinka wlewo</t>
         </is>
       </c>
     </row>

--- a/translate-PL.xlsx
+++ b/translate-PL.xlsx
@@ -4355,7 +4355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B525"/>
+  <dimension ref="A1:B526"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10655,6 +10655,18 @@
       <c r="B525" t="inlineStr">
         <is>
           <t>grafit, 80/120 x 200 cm, drabinka wlewo</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>Barva: Surové dřevo, Rozměr: 160 x 200 cm</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>surowa-b, 160 x 200 cm</t>
         </is>
       </c>
     </row>

--- a/translate-PL.xlsx
+++ b/translate-PL.xlsx
@@ -4355,7 +4355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B526"/>
+  <dimension ref="A1:B527"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10667,6 +10667,18 @@
       <c r="B526" t="inlineStr">
         <is>
           <t>surowa-b, 160 x 200 cm</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>Barva: Barva bílá, Rozměr: 90 x 180 cm, Varianta: dodat včetně zásuvek</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>bialy, 90 x 180 cm + SZ</t>
         </is>
       </c>
     </row>

--- a/translate-PL.xlsx
+++ b/translate-PL.xlsx
@@ -4355,7 +4355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B527"/>
+  <dimension ref="A1:B528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10679,6 +10679,18 @@
       <c r="B527" t="inlineStr">
         <is>
           <t>bialy, 90 x 180 cm + SZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>Barva: Barva šedá, Rozměr: 90 x 200 cm</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>popiel, 90 x 200 cm</t>
         </is>
       </c>
     </row>

--- a/translate-PL.xlsx
+++ b/translate-PL.xlsx
@@ -4355,7 +4355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B528"/>
+  <dimension ref="A1:B529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10691,6 +10691,18 @@
       <c r="B528" t="inlineStr">
         <is>
           <t>popiel, 90 x 200 cm</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>Barva: Bezbarvý lak</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>lakier</t>
         </is>
       </c>
     </row>

--- a/translate-PL.xlsx
+++ b/translate-PL.xlsx
@@ -4355,7 +4355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B529"/>
+  <dimension ref="A1:B530"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10703,6 +10703,18 @@
       <c r="B529" t="inlineStr">
         <is>
           <t>lakier</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>Barva: Surové dřevo, Délka: 140 cm</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>surowa-b, 140 cm</t>
         </is>
       </c>
     </row>

--- a/translate-PL.xlsx
+++ b/translate-PL.xlsx
@@ -11357,7 +11357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B105"/>
+  <dimension ref="A1:B106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12620,6 +12620,18 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>LP 03</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/translate-PL.xlsx
+++ b/translate-PL.xlsx
@@ -4355,7 +4355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B530"/>
+  <dimension ref="A1:B531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10715,6 +10715,18 @@
       <c r="B530" t="inlineStr">
         <is>
           <t>surowa-b, 140 cm</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>Zvolte barvu:: barva bílá, 91 cm</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>bialy, 91 cm</t>
         </is>
       </c>
     </row>

--- a/translate-PL.xlsx
+++ b/translate-PL.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B327"/>
+  <dimension ref="A1:B328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4341,6 +4341,18 @@
       <c r="B327" t="inlineStr">
         <is>
           <t>LPO 34</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Dětská postel DOMINIK PINE z masivní borovice se zábranou, roštem  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>LPO 28 + SZ</t>
         </is>
       </c>
     </row>

--- a/translate-PL.xlsx
+++ b/translate-PL.xlsx
@@ -11381,7 +11381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B106"/>
+  <dimension ref="A1:B107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12656,6 +12656,18 @@
         </is>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>LPT 03 + BARIERKA + SZ</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/translate-PL.xlsx
+++ b/translate-PL.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B328"/>
+  <dimension ref="A1:B329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4353,6 +4353,18 @@
       <c r="B328" t="inlineStr">
         <is>
           <t>LPO 28 + SZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Dětská postel DIANA PINE se zábranou, roštem  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>LPO 02 + SZ</t>
         </is>
       </c>
     </row>

--- a/translate-PL.xlsx
+++ b/translate-PL.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B329"/>
+  <dimension ref="A1:B330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4365,6 +4365,18 @@
       <c r="B329" t="inlineStr">
         <is>
           <t>LPO 02 + SZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Dětská postel KARINA PINE z masivu se zábranou, roštem  + ŠUPLÍKY</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>LPO 01 + SZ</t>
         </is>
       </c>
     </row>

--- a/translate-PL.xlsx
+++ b/translate-PL.xlsx
@@ -4391,7 +4391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B531"/>
+  <dimension ref="A1:B532"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10763,6 +10763,18 @@
       <c r="B531" t="inlineStr">
         <is>
           <t>bialy, 91 cm</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>Zvolte barvu:: barva bílá, Zvolte rozměr:: 90/120 x 200 cm, Žebřík: vlevo (vyobrazeno)</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>bialy, 90/120 x 200 cm, drabinka wlewo</t>
         </is>
       </c>
     </row>

--- a/translate-PL.xlsx
+++ b/translate-PL.xlsx
@@ -4391,7 +4391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B532"/>
+  <dimension ref="A1:B533"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10775,6 +10775,18 @@
       <c r="B532" t="inlineStr">
         <is>
           <t>bialy, 90/120 x 200 cm, drabinka wlewo</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>Zvolte barvu:: barva limetka, Zvolte rozměr:: 120 x 200 cm</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>limonka, 120 x 200 cm</t>
         </is>
       </c>
     </row>

--- a/translate-PL.xlsx
+++ b/translate-PL.xlsx
@@ -4391,7 +4391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B533"/>
+  <dimension ref="A1:B534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10787,6 +10787,18 @@
       <c r="B533" t="inlineStr">
         <is>
           <t>limonka, 120 x 200 cm</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>Zvolte barvu:: barva limetka</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>limonka</t>
         </is>
       </c>
     </row>

--- a/translate-PL.xlsx
+++ b/translate-PL.xlsx
@@ -4391,7 +4391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B534"/>
+  <dimension ref="A1:B535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10799,6 +10799,18 @@
       <c r="B534" t="inlineStr">
         <is>
           <t>limonka</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>Zvolte barvu:: barva hnědá, Zvolte rozměr:: 90 x 180 cm</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>braz, 90 x 180 cm</t>
         </is>
       </c>
     </row>

--- a/translate-PL.xlsx
+++ b/translate-PL.xlsx
@@ -11453,7 +11453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B107"/>
+  <dimension ref="A1:B108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12740,6 +12740,18 @@
         </is>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>LPO 01 + SZ</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
